--- a/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
+++ b/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
@@ -2009,7 +2009,7 @@
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mean of the available ZPI, MSI, MRI*, CRI (inverse), MH, RSI, MACD sign and volume ratio (*see the MRI defect, §6)</t>
+          <t>Mean of the available ZPI, MSI, MRI, CRI (inverse), MH, RSI, MACD sign and volume ratio (MRI was inverted until the 2026-10-26 fix, §6)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -27136,21 +27136,21 @@
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
-      <c r="G353" s="6" t="inlineStr">
-        <is>
-          <t>DEFECT</t>
+      <c r="G353" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr"/>
       <c r="I353" s="2" t="inlineStr"/>
       <c r="J353" s="2" t="inlineStr">
         <is>
-          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. But Momentum.composite inverts MRI (strategy/aggressive.py:177, :198-199), while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807)</t>
+          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. Fixed 2026-10-26: Momentum.composite inverted MRI at bed2562, while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807); MRI now enters as it is (strategy/aggressive.py:198-199)</t>
         </is>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
-          <t>Owner decision 6.1 (2): stop inverting MRI and correct the STRONG / WEAK fixtures (tests/test_aggressive_decisions.py:164-168, strategy/backtest_aggressive.py)</t>
+          <t>Done (owner decision 6.1 (2)): STRONG / WEAK fixtures mirrored, so scenario results are unchanged; a test pins the direction against determine_signal</t>
         </is>
       </c>
       <c r="L353" s="2" t="inlineStr"/>
@@ -29519,19 +29519,19 @@
           <t>Reuse existing indicators; formulas unchanged</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>DEFECT</t>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. But Momentum.composite inverts MRI (strategy/aggressive.py:177, :198-199), while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807)</t>
+          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. Fixed 2026-10-26: Momentum.composite inverted MRI at bed2562, while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807); MRI now enters as it is (strategy/aggressive.py:198-199)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Owner decision 6.1 (2): stop inverting MRI and correct the STRONG / WEAK fixtures (tests/test_aggressive_decisions.py:164-168, strategy/backtest_aggressive.py)</t>
+          <t>Done (owner decision 6.1 (2)): STRONG / WEAK fixtures mirrored, so scenario results are unchanged; a test pins the direction against determine_signal</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Correct the MRI direction in Momentum.composite (§6)</t>
+          <t>Done 2026-10-26: MRI now counts as strength in Momentum.composite (§6)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -30880,14 +30880,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Findings that need the owner's decision (details in §6):</t>
+          <t>Findings for the owner (details in §6):</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. Defect: MRI is read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487). The signal engine sells on low MRI (scores/engine.py:807). But strategy/aggressive.py:177 and :198-199 invert MRI as a risk measure. As a result, strong momentum pushes a runner toward exit and weak momentum toward holding. The tests encode the inverted reading (tests/test_aggressive_decisions.py:164-168). 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing schedules it, though: exits are managed only when python -m strategy.live --manage is run by hand. The multi-user phases (3, 5, 9, 10, 12) are only partly in place, and open PR #11 (owner-only gate) points the other way. See §6 before any new implementation starts.</t>
+          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing schedules it, though: exits are managed only when python -m strategy.live --manage is run by hand. The multi-user phases (3, 5, 9, 10, 12) are only partly in place, and open PR #11 (owner-only gate) points the other way. See §6 before any new implementation starts.</t>
         </is>
       </c>
     </row>
@@ -34910,12 +34910,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Owner decision, then fix: the MRI direction in Momentum.composite and its tests</t>
+          <t>Done 2026-10-26 (owner-approved): the MRI direction in Momentum.composite and its tests</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The runner exits on strength and holds on weakness</t>
+          <t>The runner exited on strength and held on weakness</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">

--- a/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
+++ b/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
@@ -286,7 +286,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10477500" cy="5667375"/>
+    <ext cx="10477500" cy="5972175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -27232,21 +27232,21 @@
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G355" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr"/>
       <c r="I355" s="2" t="inlineStr"/>
       <c r="J355" s="2" t="inlineStr">
         <is>
-          <t>Only python -m strategy.live --manage runs a management pass, one per call (strategy/live.py:374-410); no scheduler job or dashboard thread calls it</t>
+          <t>Scheduled 2026-10-26 (owner-approved): strategy/live.py schedule_jobs runs run_once through the scheduler's run_job every manage_interval_minutes (default 2, null = off), 09:15–15:30 on trading days, only while a position is open (no Dhan call otherwise). At bed2562 only python -m strategy.live --manage ran a pass</t>
         </is>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
-          <t>Schedule a paper management pass every few minutes in market hours, behind aggressive_enabled</t>
+          <t>The unattended pass manages only positions whose recorded mode (from the aggressive execution_mode) matches where orders now go (broker_env); the rest are reported as MODE_MISMATCH in pipeline_log, because the two switches can disagree</t>
         </is>
       </c>
       <c r="L355" s="2" t="inlineStr"/>
@@ -27289,7 +27289,7 @@
       <c r="I356" s="2" t="inlineStr"/>
       <c r="J356" s="2" t="inlineStr">
         <is>
-          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); runs only from the CLI (python -m strategy.live) and is not scheduled</t>
+          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); one scheduled pass manages every open position for the one owner</t>
         </is>
       </c>
       <c r="K356" s="2" t="inlineStr">
@@ -29583,19 +29583,19 @@
           <t>Exits managed automatically while the market is open</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Only python -m strategy.live --manage runs a management pass, one per call (strategy/live.py:374-410); no scheduler job or dashboard thread calls it</t>
+          <t>Scheduled 2026-10-26 (owner-approved): strategy/live.py schedule_jobs runs run_once through the scheduler's run_job every manage_interval_minutes (default 2, null = off), 09:15–15:30 on trading days, only while a position is open (no Dhan call otherwise). At bed2562 only python -m strategy.live --manage ran a pass</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Schedule a paper management pass every few minutes in market hours, behind aggressive_enabled</t>
+          <t>The unattended pass manages only positions whose recorded mode (from the aggressive execution_mode) matches where orders now go (broker_env); the rest are reported as MODE_MISMATCH in pipeline_log, because the two switches can disagree</t>
         </is>
       </c>
     </row>
@@ -29622,7 +29622,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); runs only from the CLI (python -m strategy.live) and is not scheduled</t>
+          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); one scheduled pass manages every open position for the one owner</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -30887,7 +30887,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing schedules it, though: exits are managed only when python -m strategy.live --manage is run by hand. The multi-user phases (3, 5, 9, 10, 12) are only partly in place, and open PR #11 (owner-only gate) points the other way. See §6 before any new implementation starts.</t>
+          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). The multi-user phases (3, 5, 9, 10, 12) are only partly in place, and open PR #11 (owner-only gate) points the other way. See §6 before any new implementation starts.</t>
         </is>
       </c>
     </row>
@@ -34964,12 +34964,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Add a "+4% profile" to the aggressive config (break-even after T1, ATR-based initial stop, time stop), and schedule the paper management pass in market hours</t>
+          <t>Add a "+4% profile" to the aggressive config (break-even after T1, ATR-based initial stop, time stop). The market-hours management pass is done (2026-10-26)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Levers 4 and 7; review row P4 (nothing runs the exits today)</t>
+          <t>Lever 4; review row P4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -35654,7 +35654,7 @@
   end
   subgraph LIVE["Market hours 09:15-15:30"]
     direction LR
-    F["every 15 min: quotes, intraday scans; 30 min: bars; WebSocket ticks; order-rule monitor"] --&gt; G["12:00 news, 12:30 ZPI scan, 14:45 pre-close scan"]
+    F["every 15 min: quotes, intraday scans; 30 min: bars; WebSocket ticks; order-rule monitor; every 2 min: aggressive exits while a position is open"] --&gt; G["12:00 news, 12:30 ZPI scan, 14:45 pre-close scan"]
     G --&gt; H["15:31 global close snapshot, 15:50 ticks EOD"]
   end
   subgraph POST["After the close"]

--- a/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
+++ b/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
@@ -49,7 +49,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Sim_Geometry'!$A$1:$K$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Sim_Policies'!$A$1:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Sim_Required_Edge'!$A$1:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Roadmap'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Roadmap'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
-          <t>Both fixes exist in PR #16 and are carried in this PR so its CI can go green</t>
+          <t>Both fixes merged with #16; master is green again from run 169</t>
         </is>
       </c>
       <c r="L335" s="2" t="inlineStr"/>
@@ -26430,7 +26430,7 @@
       </c>
       <c r="K338" s="2" t="inlineStr">
         <is>
-          <t>Decide on 6.1 (1) first</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L338" s="2" t="inlineStr"/>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
-          <t>No functional tests of login, logout, refresh or expiry; set Secure cookies on any hosted install</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26). The owner signs in through the central bkesari.com gate of PR #11 (dashboard/owner_gate.py there)</t>
         </is>
       </c>
       <c r="L339" s="2" t="inlineStr"/>
@@ -26622,7 +26622,7 @@
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
-          <t>Map ADMIN → SUPER_ADMIN of tenant default, USER → TRADER or VIEWER</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L342" s="2" t="inlineStr"/>
@@ -26670,7 +26670,7 @@
       </c>
       <c r="K343" s="2" t="inlineStr">
         <is>
-          <t>X-ATIP-Token is one install-wide secret embedded in every page (dashboard/server.py:860-862), not per user</t>
+          <t>One install-wide X-ATIP-Token fits a single owner: keep it secret and rotate it after any leak (W40 runbook)</t>
         </is>
       </c>
       <c r="L343" s="2" t="inlineStr"/>
@@ -26718,7 +26718,7 @@
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
-          <t>Leak: GET /api/orders (and /pending, /baskets, /sip) needs only execution:read (authz.py:138), which is in neither PAPER_BOOK (:152) nor FILTER_PREFIX (:175), so any tenant's VIEWER reads the owner's order rules; / embeds the owner's portfolio. No test covers cross-tenant 404s or filtering</t>
+          <t>Latent, enterprise mode only: GET /api/orders (and /pending, /baskets, /sip) needs only execution:read (enterprise/authz.py:138), in neither PAPER_BOOK (:152) nor FILTER_PREFIX (:175). Single-owner keeps enterprise mode off; fix it before it is ever switched on</t>
         </is>
       </c>
       <c r="L344" s="2" t="inlineStr"/>
@@ -26766,7 +26766,7 @@
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
-          <t>Add owner scoping per table, or keep one user per tenant</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L345" s="2" t="inlineStr"/>
@@ -26814,7 +26814,7 @@
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
-          <t>Only read-only connectors use it (brokers/registry.py:37-72); orders, market data and the strategy use the owner's global client (orders/broker.py:157,272); a default-tenant user without a vault entry silently gets the owner's credentials (enterprise/vault.py:184-187)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26): the owner's credentials stay in config.json / the vault</t>
         </is>
       </c>
       <c r="L346" s="2" t="inlineStr"/>
@@ -26910,7 +26910,7 @@
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
-          <t>No per-user layout, widgets or theme; the main page is rendered without knowing the user (dashboard/server.py:1339-1341)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L348" s="2" t="inlineStr"/>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
-          <t>No test that a non-admin is refused</t>
+          <t>Not applicable with one owner</t>
         </is>
       </c>
       <c r="L349" s="2" t="inlineStr"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>Needs user / tenant columns, per-user config and per-user broker routing, after 6.1 (1)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L356" s="2" t="inlineStr"/>
@@ -27486,7 +27486,7 @@
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
-          <t>Write them once 6.1 (1) is decided</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26); PR #11 tests the owner gate (tests/test_owner_gate.py there)</t>
         </is>
       </c>
       <c r="L360" s="2" t="inlineStr"/>
@@ -27534,7 +27534,7 @@
       </c>
       <c r="K361" s="2" t="inlineStr">
         <is>
-          <t>Add cross-tenant 404 / filter tests, including /api/orders</t>
+          <t>Only if enterprise mode is ever switched on (with the /api/orders fix, row P3)</t>
         </is>
       </c>
       <c r="L361" s="2" t="inlineStr"/>
@@ -27582,7 +27582,7 @@
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
-          <t>After P3 / P5</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L362" s="2" t="inlineStr"/>
@@ -27616,9 +27616,9 @@
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr"/>
-      <c r="G363" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr"/>
@@ -27630,7 +27630,7 @@
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
-          <t>master is red on the two tests in row P1</t>
+          <t>master green from run 169 (#16); this branch 1,578 passed, 0 failed</t>
         </is>
       </c>
       <c r="L363" s="2" t="inlineStr"/>
@@ -27774,7 +27774,7 @@
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
-          <t>Add a read-only "Aggressive positions" panel and API</t>
+          <t>Single-owner: the existing dashboard behind the owner gate. Still worth adding: a read-only "Aggressive positions" panel and API</t>
         </is>
       </c>
       <c r="L366" s="2" t="inlineStr"/>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Both fixes exist in PR #16 and are carried in this PR so its CI can go green</t>
+          <t>Both fixes merged with #16; master is green again from run 169</t>
         </is>
       </c>
     </row>
@@ -29051,7 +29051,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Decide on 6.1 (1) first</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>No functional tests of login, logout, refresh or expiry; set Secure cookies on any hosted install</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26). The owner signs in through the central bkesari.com gate of PR #11 (dashboard/owner_gate.py there)</t>
         </is>
       </c>
     </row>
@@ -29179,7 +29179,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Map ADMIN → SUPER_ADMIN of tenant default, USER → TRADER or VIEWER</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29211,7 +29211,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>X-ATIP-Token is one install-wide secret embedded in every page (dashboard/server.py:860-862), not per user</t>
+          <t>One install-wide X-ATIP-Token fits a single owner: keep it secret and rotate it after any leak (W40 runbook)</t>
         </is>
       </c>
     </row>
@@ -29243,7 +29243,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Leak: GET /api/orders (and /pending, /baskets, /sip) needs only execution:read (authz.py:138), which is in neither PAPER_BOOK (:152) nor FILTER_PREFIX (:175), so any tenant's VIEWER reads the owner's order rules; / embeds the owner's portfolio. No test covers cross-tenant 404s or filtering</t>
+          <t>Latent, enterprise mode only: GET /api/orders (and /pending, /baskets, /sip) needs only execution:read (enterprise/authz.py:138), in neither PAPER_BOOK (:152) nor FILTER_PREFIX (:175). Single-owner keeps enterprise mode off; fix it before it is ever switched on</t>
         </is>
       </c>
     </row>
@@ -29275,7 +29275,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Add owner scoping per table, or keep one user per tenant</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Only read-only connectors use it (brokers/registry.py:37-72); orders, market data and the strategy use the owner's global client (orders/broker.py:157,272); a default-tenant user without a vault entry silently gets the owner's credentials (enterprise/vault.py:184-187)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26): the owner's credentials stay in config.json / the vault</t>
         </is>
       </c>
     </row>
@@ -29371,7 +29371,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>No per-user layout, widgets or theme; the main page is rendered without knowing the user (dashboard/server.py:1339-1341)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>No test that a non-admin is refused</t>
+          <t>Not applicable with one owner</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Needs user / tenant columns, per-user config and per-user broker routing, after 6.1 (1)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29755,7 +29755,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Write them once 6.1 (1) is decided</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26); PR #11 tests the owner gate (tests/test_owner_gate.py there)</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Add cross-tenant 404 / filter tests, including /api/orders</t>
+          <t>Only if enterprise mode is ever switched on (with the /api/orders fix, row P3)</t>
         </is>
       </c>
     </row>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>After P3 / P5</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29839,9 +29839,9 @@
           <t>Full regression stays green</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>master is red on the two tests in row P1</t>
+          <t>master green from run 169 (#16); this branch 1,578 passed, 0 failed</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Add a read-only "Aggressive positions" panel and API</t>
+          <t>Single-owner: the existing dashboard behind the owner gate. Still worth adding: a read-only "Aggressive positions" panel and API</t>
         </is>
       </c>
     </row>
@@ -30887,7 +30887,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). The multi-user phases (3, 5, 9, 10, 12) are only partly in place, and open PR #11 (owner-only gate) points the other way. See §6 before any new implementation starts.</t>
+          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). Decided 2026-10-26: ATIP stays single-owner, in line with PR #11's owner-only gate, so the prompt's multi-user phases (3, 5 and the per-user parts of 7 and 9) are not planned. See §6.</t>
         </is>
       </c>
     </row>
@@ -34860,7 +34860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35121,22 +35121,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Multi-user items from §6 (only if a multi-user product is wanted)</t>
+          <t>Dropped 2026-10-26: multi-user items from §6. ATIP stays single-owner (owner decision)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Consolidated-prompt phases 3, 5, 9, 10</t>
+          <t>Consolidated-prompt phases 3, 5 and the per-user parts of 7 and 9</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -35153,12 +35153,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Deploy to test.bkesari.com/dhan once hosting and secrets are decided</t>
+          <t>Deploy the single-owner ATIP to test.bkesari.com behind the owner gate (PR #11), with the base-path fix, once hosting and secrets are decided</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Consolidated-prompt phase 10</t>
+          <t>Consolidated-prompt phase 10, decision 6.1 (3)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -35167,8 +35167,35 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Close the latent /api/orders read leak in enterprise/authz.py (enterprise mode only)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Review row P3; matters only if enterprise mode is ever switched on</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
+++ b/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
@@ -38,9 +38,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Architecture_Layers'!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Diagrams'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Terminology'!$A$1:$E$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Features'!$A$1:$N$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Features'!$A$1:$N$373</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Feature_Summary'!$A$1:$F$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Prompt_Review'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Prompt_Review'!$A$1:$F$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Objective_Arithmetic'!$A$1:$D$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Objective_Verdict'!$A$1:$C$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Levers'!$A$1:$E$9</definedName>
@@ -49,7 +49,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Sim_Geometry'!$A$1:$K$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Sim_Policies'!$A$1:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Sim_Required_Edge'!$A$1:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Roadmap'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Roadmap'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3466,7 +3466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N372"/>
+  <dimension ref="A1:N373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26718,7 +26718,7 @@
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
-          <t>Latent, enterprise mode only: GET /api/orders (and /pending, /baskets, /sip) needs only execution:read (enterprise/authz.py:138), in neither PAPER_BOOK (:152) nor FILTER_PREFIX (:175). Single-owner keeps enterprise mode off; fix it before it is ever switched on</t>
+          <t>Fixed 2026-10-26: OWNER_BOOK in enterprise/authz.py refuses the owner's book to any other tenant, whatever its role (/api/orders with baskets, SIPs and broker status; /api/oms/positions; /api/mobile/; /api/risk/ limits, portfolio, emergency exit and evaluation), and sends another tenant from / to /app. Before the fix, eight GET routes showed the owner's book to another tenant's viewer, and PUT /api/risk/limits and POST /api/risk/emergency-exit were open to a tenant's risk manager. tests/test_enterprise_owner_book.py checks every GET route with canary data in every owner table</t>
         </is>
       </c>
       <c r="L344" s="2" t="inlineStr"/>
@@ -26882,35 +26882,35 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Personalization</t>
+          <t>Secrets</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Per-user widgets, layout, watchlist, theme, preferences</t>
+          <t>The install-wide dashboard token must not reach another tenant</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>Per-user widgets, layout, watchlist, theme, preferences</t>
+          <t>The install-wide dashboard token must not reach another tenant</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
-      <c r="G348" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="G348" s="6" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr"/>
       <c r="I348" s="2" t="inlineStr"/>
       <c r="J348" s="2" t="inlineStr">
         <is>
-          <t>Per-user watchlists, alerts and reports with ownership checks (enterprise/workspace.py:33-135); notification preferences; preferences_json stored but never read (enterprise/users.py:160-170)</t>
+          <t>Measured 2026-10-26: 18 HTML pages return the token to another tenant's VIEWER (/backtests, /strategies, /trading, /market, /execution-lab, /data-platform, /assistant, /strategy-builder, /brokers, /compliance, /research, /options-builder, /market-pulse, /signals, /screener, /baskets, /ml, /wealth); the token is the X-ATIP-Token that guards the write routes (dashboard/security.py)</t>
         </is>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
+          <t>Open (R12). Per-user or per-session tokens, or no token in pages served to other tenants. Enterprise mode is off, so this is latent</t>
         </is>
       </c>
       <c r="L348" s="2" t="inlineStr"/>
@@ -26935,12 +26935,12 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Ordinary users cannot change global formulas / config</t>
+          <t>Per-user widgets, layout, watchlist, theme, preferences</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>Ordinary users cannot change global formulas / config</t>
+          <t>Per-user widgets, layout, watchlist, theme, preferences</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr"/>
@@ -26953,12 +26953,12 @@
       <c r="I349" s="2" t="inlineStr"/>
       <c r="J349" s="2" t="inlineStr">
         <is>
-          <t>Default-deny permissions; weight_config changes need operator permissions</t>
+          <t>Per-user watchlists, alerts and reports with ownership checks (enterprise/workspace.py:33-135); notification preferences; preferences_json stored but never read (enterprise/users.py:160-170)</t>
         </is>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
-          <t>Not applicable with one owner</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L349" s="2" t="inlineStr"/>
@@ -26968,7 +26968,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-04-01</t>
+          <t>CP-03-13</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -26978,35 +26978,35 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Personalization</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>+3% sells 50% of the original quantity, runner kept, trail starts</t>
+          <t>Ordinary users cannot change global formulas / config</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>+3% sells 50% of the original quantity, runner kept, trail starts</t>
+          <t>Ordinary users cannot change global formulas / config</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr"/>
-      <c r="G350" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+      <c r="G350" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr"/>
       <c r="I350" s="2" t="inlineStr"/>
       <c r="J350" s="2" t="inlineStr">
         <is>
-          <t>strategy/aggressive.py (partial_exit_quantity, ratchet), strategy/positions.py (idempotent claims); tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py</t>
+          <t>Default-deny permissions; weight_config changes need operator permissions</t>
         </is>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not applicable with one owner</t>
         </is>
       </c>
       <c r="L350" s="2" t="inlineStr"/>
@@ -27016,7 +27016,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>CP-04-02</t>
+          <t>CP-04-01</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -27031,12 +27031,12 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>+6% is a momentum checkpoint, not a forced exit</t>
+          <t>+3% sells 50% of the original quantity, runner kept, trail starts</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>+6% is a momentum checkpoint, not a forced exit</t>
+          <t>+3% sells 50% of the original quantity, runner kept, trail starts</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr"/>
@@ -27049,7 +27049,7 @@
       <c r="I351" s="2" t="inlineStr"/>
       <c r="J351" s="2" t="inlineStr">
         <is>
-          <t>checkpoint_decision: HOLD_RUNNER ≥ 60, TIGHTEN_TRAIL 40–60 or no data, EXIT_RUNNER &lt; 40</t>
+          <t>strategy/aggressive.py (partial_exit_quantity, ratchet), strategy/positions.py (idempotent claims); tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py</t>
         </is>
       </c>
       <c r="K351" s="2" t="inlineStr">
@@ -27064,7 +27064,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-04-03</t>
+          <t>CP-04-02</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -27079,12 +27079,12 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Levels configurable, validated (40/60, 60/40; invalid rejected)</t>
+          <t>+6% is a momentum checkpoint, not a forced exit</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>Levels configurable, validated (40/60, 60/40; invalid rejected)</t>
+          <t>+6% is a momentum checkpoint, not a forced exit</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
@@ -27097,7 +27097,7 @@
       <c r="I352" s="2" t="inlineStr"/>
       <c r="J352" s="2" t="inlineStr">
         <is>
-          <t>DEFAULTS + config.json + validate_config (strategy/aggressive.py:50-130)</t>
+          <t>checkpoint_decision: HOLD_RUNNER ≥ 60, TIGHTEN_TRAIL 40–60 or no data, EXIT_RUNNER &lt; 40</t>
         </is>
       </c>
       <c r="K352" s="2" t="inlineStr">
@@ -27112,7 +27112,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>CP-04-04</t>
+          <t>CP-04-03</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -27127,12 +27127,12 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Reuse existing indicators; formulas unchanged</t>
+          <t>Levels configurable, validated (40/60, 60/40; invalid rejected)</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>Reuse existing indicators; formulas unchanged</t>
+          <t>Levels configurable, validated (40/60, 60/40; invalid rejected)</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
@@ -27145,12 +27145,12 @@
       <c r="I353" s="2" t="inlineStr"/>
       <c r="J353" s="2" t="inlineStr">
         <is>
-          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. Fixed 2026-10-26: Momentum.composite inverted MRI at bed2562, while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807); MRI now enters as it is (strategy/aggressive.py:198-199)</t>
+          <t>DEFAULTS + config.json + validate_config (strategy/aggressive.py:50-130)</t>
         </is>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
-          <t>Done (owner decision 6.1 (2)): STRONG / WEAK fixtures mirrored, so scenario results are unchanged; a test pins the direction against determine_signal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L353" s="2" t="inlineStr"/>
@@ -27160,7 +27160,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-04-05</t>
+          <t>CP-04-04</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Volatility-aware trail that never moves down</t>
+          <t>Reuse existing indicators; formulas unchanged</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>Volatility-aware trail that never moves down</t>
+          <t>Reuse existing indicators; formulas unchanged</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
@@ -27193,12 +27193,12 @@
       <c r="I354" s="2" t="inlineStr"/>
       <c r="J354" s="2" t="inlineStr">
         <is>
-          <t>4 × ATR%, clamped 3–20%; ratchet is one-way; tightens ×0.5 on fading momentum</t>
+          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. Fixed 2026-10-26: Momentum.composite inverted MRI at bed2562, while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807); MRI now enters as it is (strategy/aggressive.py:198-199)</t>
         </is>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Done (owner decision 6.1 (2)): STRONG / WEAK fixtures mirrored, so scenario results are unchanged; a test pins the direction against determine_signal</t>
         </is>
       </c>
       <c r="L354" s="2" t="inlineStr"/>
@@ -27208,7 +27208,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>CP-04-06</t>
+          <t>CP-04-05</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -27223,12 +27223,12 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Exits managed automatically while the market is open</t>
+          <t>Volatility-aware trail that never moves down</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>Exits managed automatically while the market is open</t>
+          <t>Volatility-aware trail that never moves down</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
@@ -27241,12 +27241,12 @@
       <c r="I355" s="2" t="inlineStr"/>
       <c r="J355" s="2" t="inlineStr">
         <is>
-          <t>Scheduled 2026-10-26 (owner-approved): strategy/live.py schedule_jobs runs run_once through the scheduler's run_job every manage_interval_minutes (default 2, null = off), 09:15–15:30 on trading days, only while a position is open (no Dhan call otherwise). At bed2562 only python -m strategy.live --manage ran a pass</t>
+          <t>4 × ATR%, clamped 3–20%; ratchet is one-way; tightens ×0.5 on fading momentum</t>
         </is>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
-          <t>The unattended pass manages only positions whose recorded mode (from the aggressive execution_mode) matches where orders now go (broker_env); the rest are reported as MODE_MISMATCH in pipeline_log, because the two switches can disagree</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L355" s="2" t="inlineStr"/>
@@ -27256,7 +27256,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-05-01</t>
+          <t>CP-04-06</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -27266,35 +27266,35 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Per user</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Same signal, private execution state per user (own entry, qty, trail)</t>
+          <t>Exits managed automatically while the market is open</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>Same signal, private execution state per user (own entry, qty, trail)</t>
+          <t>Exits managed automatically while the market is open</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr"/>
-      <c r="G356" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G356" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr"/>
       <c r="I356" s="2" t="inlineStr"/>
       <c r="J356" s="2" t="inlineStr">
         <is>
-          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); one scheduled pass manages every open position for the one owner</t>
+          <t>Scheduled 2026-10-26 (owner-approved): strategy/live.py schedule_jobs runs run_once through the scheduler's run_job every manage_interval_minutes (default 2, null = off), 09:15–15:30 on trading days, only while a position is open (no Dhan call otherwise). At bed2562 only python -m strategy.live --manage ran a pass</t>
         </is>
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
+          <t>The unattended pass manages only positions whose recorded mode (from the aggressive execution_mode) matches where orders now go (broker_env); the rest are reported as MODE_MISMATCH in pipeline_log, because the two switches can disagree</t>
         </is>
       </c>
       <c r="L356" s="2" t="inlineStr"/>
@@ -27304,7 +27304,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>CP-06-01</t>
+          <t>CP-05-01</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -27314,35 +27314,35 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Per user</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Initial / remaining / partial quantity, T1 / T2 state, high water, trail, realised / unrealised P&amp;L, exit reason</t>
+          <t>Same signal, private execution state per user (own entry, qty, trail)</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>Initial / remaining / partial quantity, T1 / T2 state, high water, trail, realised / unrealised P&amp;L, exit reason</t>
+          <t>Same signal, private execution state per user (own entry, qty, trail)</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr"/>
-      <c r="G357" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+      <c r="G357" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr"/>
       <c r="I357" s="2" t="inlineStr"/>
       <c r="J357" s="2" t="inlineStr">
         <is>
-          <t>strategy_position columns (strategy/positions.py:37-84): initial_qty, remaining_qty, t1_state/qty/price/at, t2_state/at, high_water, trail_pct/stop/moves, realized_pnl, unrealized_pnl, exit_reason, mode</t>
+          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); one scheduled pass manages every open position for the one owner</t>
         </is>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L357" s="2" t="inlineStr"/>
@@ -27352,7 +27352,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-06-02</t>
+          <t>CP-06-01</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -27367,12 +27367,12 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Machine-readable exit reasons</t>
+          <t>Initial / remaining / partial quantity, T1 / T2 state, high water, trail, realised / unrealised P&amp;L, exit reason</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>Machine-readable exit reasons</t>
+          <t>Initial / remaining / partial quantity, T1 / T2 state, high water, trail, realised / unrealised P&amp;L, exit reason</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       <c r="I358" s="2" t="inlineStr"/>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>The 8 constants in strategy/aggressive.py</t>
+          <t>strategy_position columns (strategy/positions.py:37-84): initial_qty, remaining_qty, t1_state/qty/price/at, t2_state/at, high_water, trail_pct/stop/moves, realized_pnl, unrealized_pnl, exit_reason, mode</t>
         </is>
       </c>
       <c r="K358" s="2" t="inlineStr">
@@ -27400,7 +27400,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>CP-07-01</t>
+          <t>CP-06-02</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -27410,17 +27410,17 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Aggressive strategy tests (config, entry, SL, +3%, runner, +6%, trail, idempotency, broker, edge cases)</t>
+          <t>Machine-readable exit reasons</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>Aggressive strategy tests (config, entry, SL, +3%, runner, +6%, trail, idempotency, broker, edge cases)</t>
+          <t>Machine-readable exit reasons</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
@@ -27433,7 +27433,7 @@
       <c r="I359" s="2" t="inlineStr"/>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py, test_aggressive_backtest.py, test_strategy_live.py, test_paper_broker.py</t>
+          <t>The 8 constants in strategy/aggressive.py</t>
         </is>
       </c>
       <c r="K359" s="2" t="inlineStr">
@@ -27448,7 +27448,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-07-02</t>
+          <t>CP-07-01</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -27463,30 +27463,30 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Authentication tests</t>
+          <t>Aggressive strategy tests (config, entry, SL, +3%, runner, +6%, trail, idempotency, broker, edge cases)</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>Authentication tests</t>
+          <t>Aggressive strategy tests (config, entry, SL, +3%, runner, +6%, trail, idempotency, broker, edge cases)</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr"/>
-      <c r="G360" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr"/>
       <c r="I360" s="2" t="inlineStr"/>
       <c r="J360" s="2" t="inlineStr">
         <is>
-          <t>Only route labels are checked (tests/test_w39_ops_tests.py:722-750)</t>
+          <t>tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py, test_aggressive_backtest.py, test_strategy_live.py, test_paper_broker.py</t>
         </is>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26); PR #11 tests the owner gate (tests/test_owner_gate.py there)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L360" s="2" t="inlineStr"/>
@@ -27496,7 +27496,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>CP-07-03</t>
+          <t>CP-07-02</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -27511,30 +27511,30 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Authorization / cross-user security tests</t>
+          <t>Authentication tests</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>Authorization / cross-user security tests</t>
+          <t>Authentication tests</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
-      <c r="G361" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="G361" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr"/>
       <c r="I361" s="2" t="inlineStr"/>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>tests/test_wealth_api_security.py (8), cross-owner wealth tests, tenant book test</t>
+          <t>Only route labels are checked (tests/test_w39_ops_tests.py:722-750)</t>
         </is>
       </c>
       <c r="K361" s="2" t="inlineStr">
         <is>
-          <t>Only if enterprise mode is ever switched on (with the /api/orders fix, row P3)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26); PR #11 tests the owner gate (tests/test_owner_gate.py there)</t>
         </is>
       </c>
       <c r="L361" s="2" t="inlineStr"/>
@@ -27544,7 +27544,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-07-04</t>
+          <t>CP-07-03</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -27559,30 +27559,30 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Dhan isolation and personalization tests</t>
+          <t>Authorization / cross-user security tests</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>Dhan isolation and personalization tests</t>
+          <t>Authorization / cross-user security tests</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
-      <c r="G362" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G362" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr"/>
       <c r="I362" s="2" t="inlineStr"/>
       <c r="J362" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tests/test_wealth_api_security.py (8), cross-owner wealth tests, tenant book test</t>
         </is>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
+          <t>tests/test_enterprise_owner_book.py (7) and tests/test_wealth_api_security.py (8); the owner-book scan covers every GET route</t>
         </is>
       </c>
       <c r="L362" s="2" t="inlineStr"/>
@@ -27592,7 +27592,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>CP-07-05</t>
+          <t>CP-07-04</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -27607,30 +27607,30 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Full regression stays green</t>
+          <t>Dhan isolation and personalization tests</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>Full regression stays green</t>
+          <t>Dhan isolation and personalization tests</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr"/>
-      <c r="G363" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+      <c r="G363" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr"/>
       <c r="I363" s="2" t="inlineStr"/>
       <c r="J363" s="2" t="inlineStr">
         <is>
-          <t>1,315 test functions in 85 files; CI python -m pytest tests/ -v + scenario replay</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
-          <t>master green from run 169 (#16); this branch 1,578 passed, 0 failed</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
       <c r="L363" s="2" t="inlineStr"/>
@@ -27640,7 +27640,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-08-01</t>
+          <t>CP-07-05</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -27650,17 +27650,17 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Backtest</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>The 7 deterministic scenarios and the full metric list</t>
+          <t>Full regression stays green</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>The 7 deterministic scenarios and the full metric list</t>
+          <t>Full regression stays green</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
@@ -27673,12 +27673,12 @@
       <c r="I364" s="2" t="inlineStr"/>
       <c r="J364" s="2" t="inlineStr">
         <is>
-          <t>strategy/backtest_aggressive.scenarios() and metrics(): win rate, PF, expectancy, drawdown, T1 / T2 rates, runner success, trailing / initial-stop exit rates, profit after +3%</t>
+          <t>1,315 test functions in 85 files; CI python -m pytest tests/ -v + scenario replay</t>
         </is>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>master green from run 169 (#16); this branch 1,578 passed, 0 failed</t>
         </is>
       </c>
       <c r="L364" s="2" t="inlineStr"/>
@@ -27688,7 +27688,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>CP-08-02</t>
+          <t>CP-08-01</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -27703,12 +27703,12 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Do not claim profitability unless shown after costs</t>
+          <t>The 7 deterministic scenarios and the full metric list</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>Do not claim profitability unless shown after costs</t>
+          <t>The 7 deterministic scenarios and the full metric list</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr"/>
@@ -27721,12 +27721,12 @@
       <c r="I365" s="2" t="inlineStr"/>
       <c r="J365" s="2" t="inlineStr">
         <is>
-          <t>Costs on every leg, same-bar ambiguity against the strategy; the real-bars comparison is strategy/backtest_history.py</t>
+          <t>strategy/backtest_aggressive.scenarios() and metrics(): win rate, PF, expectancy, drawdown, T1 / T2 rates, runner success, trailing / initial-stop exit rates, profit after +3%</t>
         </is>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
-          <t>Run it on the real database (§7.8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L365" s="2" t="inlineStr"/>
@@ -27736,7 +27736,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-09-01</t>
+          <t>CP-08-02</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -27746,35 +27746,35 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Backtest</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Private dashboard at /dhan after login, with aggressive-trade state</t>
+          <t>Do not claim profitability unless shown after costs</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>Private dashboard at /dhan after login, with aggressive-trade state</t>
+          <t>Do not claim profitability unless shown after costs</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr"/>
-      <c r="G366" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G366" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr"/>
       <c r="I366" s="2" t="inlineStr"/>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>No /dhan base path anywhere; strategy_position is not shown in any page or API, only via python -m strategy.live status</t>
+          <t>Costs on every leg, same-bar ambiguity against the strategy; the real-bars comparison is strategy/backtest_history.py</t>
         </is>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
-          <t>Single-owner: the existing dashboard behind the owner gate. Still worth adding: a read-only "Aggressive positions" panel and API</t>
+          <t>Run it on the real database (§7.8)</t>
         </is>
       </c>
       <c r="L366" s="2" t="inlineStr"/>
@@ -27784,7 +27784,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>CP-09-02</t>
+          <t>CP-09-01</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -27794,35 +27794,35 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>App works under a base path</t>
+          <t>Private dashboard at /dhan after login, with aggressive-trade state</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>App works under a base path</t>
+          <t>Private dashboard at /dhan after login, with aggressive-trade state</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr"/>
-      <c r="G367" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="G367" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr"/>
       <c r="I367" s="2" t="inlineStr"/>
       <c r="J367" s="2" t="inlineStr">
         <is>
-          <t>ATIP_ROOT_PATH / dashboard_root_path (dashboard/security.py:86-102, main.py:481-487); docs use /ATIP</t>
+          <t>No /dhan base path anywhere; strategy_position is not shown in any page or API, only via python -m strategy.live status</t>
         </is>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
-          <t>Page JavaScript calls absolute /api/... and the login redirect is a bare /login (enterprise/authz.py:265), so the browser leaves the prefix (also PR #14's open D10)</t>
+          <t>Single-owner: the existing dashboard behind the owner gate. Still worth adding: a read-only "Aggressive positions" panel and API</t>
         </is>
       </c>
       <c r="L367" s="2" t="inlineStr"/>
@@ -27832,7 +27832,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-10-01</t>
+          <t>CP-09-02</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -27842,17 +27842,17 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Deploy</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Container, health check, test/production separation, externalized secrets</t>
+          <t>App works under a base path</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>Container, health check, test/production separation, externalized secrets</t>
+          <t>App works under a base path</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr"/>
@@ -27865,12 +27865,12 @@
       <c r="I368" s="2" t="inlineStr"/>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>Dockerfile (non-root, HEALTHCHECK), docker-compose.yml on 127.0.0.1, /health/live and /health/ready; CI builds and boots the image</t>
+          <t>ATIP_ROOT_PATH / dashboard_root_path (dashboard/security.py:86-102, main.py:481-487); docs use /ATIP</t>
         </is>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
-          <t>No deploy workflow, no TLS proxy, no trusted-hosts check, rate limiting off; HSTS / Secure cookies only with ops.tls_enabled; Python 3.12 in CI vs 3.14 in Docker</t>
+          <t>Page JavaScript calls absolute /api/... and the login redirect is a bare /login (enterprise/authz.py:265), so the browser leaves the prefix (also PR #14's open D10)</t>
         </is>
       </c>
       <c r="L368" s="2" t="inlineStr"/>
@@ -27880,7 +27880,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>CP-10-02</t>
+          <t>CP-10-01</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -27895,30 +27895,30 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Deploy to test.bkesari.com/dhan</t>
+          <t>Container, health check, test/production separation, externalized secrets</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>Deploy to test.bkesari.com/dhan</t>
+          <t>Container, health check, test/production separation, externalized secrets</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G369" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr"/>
       <c r="I369" s="2" t="inlineStr"/>
       <c r="J369" s="2" t="inlineStr">
         <is>
-          <t>test.bkesari.com receives only the snapshot</t>
+          <t>Dockerfile (non-root, HEALTHCHECK), docker-compose.yml on 127.0.0.1, /health/live and /health/ready; CI builds and boots the image</t>
         </is>
       </c>
       <c r="K369" s="2" t="inlineStr">
         <is>
-          <t>Needs 6.1 (3) and the owner's hosting credentials</t>
+          <t>No deploy workflow, no TLS proxy, no trusted-hosts check, rate limiting off; HSTS / Secure cookies only with ops.tls_enabled; Python 3.12 in CI vs 3.14 in Docker</t>
         </is>
       </c>
       <c r="L369" s="2" t="inlineStr"/>
@@ -27928,7 +27928,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-11-01</t>
+          <t>CP-10-02</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -27938,35 +27938,35 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Deploy</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Grouped commits, no secrets committed, push to the branch</t>
+          <t>Deploy to test.bkesari.com/dhan</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>Grouped commits, no secrets committed, push to the branch</t>
+          <t>Deploy to test.bkesari.com/dhan</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+      <c r="G370" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr"/>
       <c r="I370" s="2" t="inlineStr"/>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>Branch per change with draft PRs; atip_data/, .env and deploy/atip.env are git-ignored</t>
+          <t>test.bkesari.com receives only the snapshot</t>
         </is>
       </c>
       <c r="K370" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Needs 6.1 (3) and the owner's hosting credentials</t>
         </is>
       </c>
       <c r="L370" s="2" t="inlineStr"/>
@@ -27976,7 +27976,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>CP-12-01</t>
+          <t>CP-11-01</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -27986,35 +27986,35 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Post-deployment checks on the test URL</t>
+          <t>Grouped commits, no secrets committed, push to the branch</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>Post-deployment checks on the test URL</t>
+          <t>Grouped commits, no secrets committed, push to the branch</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
-      <c r="G371" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+      <c r="G371" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr"/>
       <c r="I371" s="2" t="inlineStr"/>
       <c r="J371" s="2" t="inlineStr">
         <is>
-          <t>Nothing is deployed</t>
+          <t>Branch per change with draft PRs; atip_data/, .env and deploy/atip.env are git-ignored</t>
         </is>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
-          <t>After P10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L371" s="2" t="inlineStr"/>
@@ -28024,7 +28024,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-13-01</t>
+          <t>CP-12-01</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -28034,43 +28034,91 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Paper by default; no live orders from a test deployment</t>
+          <t>Post-deployment checks on the test URL</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>Paper by default; no live orders from a test deployment</t>
+          <t>Post-deployment checks on the test URL</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr"/>
-      <c r="G372" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+      <c r="G372" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr"/>
       <c r="I372" s="2" t="inlineStr"/>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>broker_env falls back to PAPER (orders/environment.py:43-53); LIVE needs confirm, no halt, execution.live_trading_enabled and environment production (ops/trading_safety.py:24-42); the execution layer's Dhan adapter refuses every call (execution/adapters.py:240-260)</t>
+          <t>Nothing is deployed</t>
         </is>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
-          <t>deploy/atip.env.example:5 sets ATIP_ENV=production, so a container built from the example already meets one LIVE condition: set it to staging for test.bkesari.com</t>
+          <t>After P10</t>
         </is>
       </c>
       <c r="L372" s="2" t="inlineStr"/>
       <c r="M372" s="2" t="inlineStr"/>
       <c r="N372" s="2" t="inlineStr"/>
     </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>CP-13-01</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated prompt (2026-10-26)</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Paper by default; no live orders from a test deployment</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Paper by default; no live orders from a test deployment</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr"/>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr"/>
+      <c r="I373" s="2" t="inlineStr"/>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>broker_env falls back to PAPER (orders/environment.py:43-53); LIVE needs confirm, no halt, execution.live_trading_enabled and environment production (ops/trading_safety.py:24-42); the execution layer's Dhan adapter refuses every call (execution/adapters.py:240-260)</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>deploy/atip.env.example:5 sets ATIP_ENV=production, so a container built from the example already meets one LIVE condition: set it to staging for test.bkesari.com</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr"/>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N372"/>
+  <autoFilter ref="A1:N373"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28884,7 +28932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29243,7 +29291,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Latent, enterprise mode only: GET /api/orders (and /pending, /baskets, /sip) needs only execution:read (enterprise/authz.py:138), in neither PAPER_BOOK (:152) nor FILTER_PREFIX (:175). Single-owner keeps enterprise mode off; fix it before it is ever switched on</t>
+          <t>Fixed 2026-10-26: OWNER_BOOK in enterprise/authz.py refuses the owner's book to any other tenant, whatever its role (/api/orders with baskets, SIPs and broker status; /api/oms/positions; /api/mobile/; /api/risk/ limits, portfolio, emergency exit and evaluation), and sends another tenant from / to /app. Before the fix, eight GET routes showed the owner's book to another tenant's viewer, and PUT /api/risk/limits and POST /api/risk/emergency-exit were open to a tenant's risk manager. tests/test_enterprise_owner_book.py checks every GET route with canary data in every owner table</t>
         </is>
       </c>
     </row>
@@ -29351,27 +29399,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Personalization</t>
+          <t>Secrets</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Per-user widgets, layout, watchlist, theme, preferences</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>The install-wide dashboard token must not reach another tenant</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Per-user watchlists, alerts and reports with ownership checks (enterprise/workspace.py:33-135); notification preferences; preferences_json stored but never read (enterprise/users.py:160-170)</t>
+          <t>Measured 2026-10-26: 18 HTML pages return the token to another tenant's VIEWER (/backtests, /strategies, /trading, /market, /execution-lab, /data-platform, /assistant, /strategy-builder, /brokers, /compliance, /research, /options-builder, /market-pulse, /signals, /screener, /baskets, /ml, /wealth); the token is the X-ATIP-Token that guards the write routes (dashboard/security.py)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
+          <t>Open (R12). Per-user or per-session tokens, or no token in pages served to other tenants. Enterprise mode is off, so this is latent</t>
         </is>
       </c>
     </row>
@@ -29388,7 +29436,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Ordinary users cannot change global formulas / config</t>
+          <t>Per-user widgets, layout, watchlist, theme, preferences</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -29398,44 +29446,44 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Default-deny permissions; weight_config changes need operator permissions</t>
+          <t>Per-user watchlists, alerts and reports with ownership checks (enterprise/workspace.py:33-135); notification preferences; preferences_json stored but never read (enterprise/users.py:160-170)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Not applicable with one owner</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Personalization</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+3% sells 50% of the original quantity, runner kept, trail starts</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+          <t>Ordinary users cannot change global formulas / config</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>strategy/aggressive.py (partial_exit_quantity, ratchet), strategy/positions.py (idempotent claims); tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py</t>
+          <t>Default-deny permissions; weight_config changes need operator permissions</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not applicable with one owner</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29500,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+6% is a momentum checkpoint, not a forced exit</t>
+          <t>+3% sells 50% of the original quantity, runner kept, trail starts</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -29462,7 +29510,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>checkpoint_decision: HOLD_RUNNER ≥ 60, TIGHTEN_TRAIL 40–60 or no data, EXIT_RUNNER &lt; 40</t>
+          <t>strategy/aggressive.py (partial_exit_quantity, ratchet), strategy/positions.py (idempotent claims); tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -29484,7 +29532,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Levels configurable, validated (40/60, 60/40; invalid rejected)</t>
+          <t>+6% is a momentum checkpoint, not a forced exit</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -29494,7 +29542,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DEFAULTS + config.json + validate_config (strategy/aggressive.py:50-130)</t>
+          <t>checkpoint_decision: HOLD_RUNNER ≥ 60, TIGHTEN_TRAIL 40–60 or no data, EXIT_RUNNER &lt; 40</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -29516,7 +29564,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Reuse existing indicators; formulas unchanged</t>
+          <t>Levels configurable, validated (40/60, 60/40; invalid rejected)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -29526,12 +29574,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. Fixed 2026-10-26: Momentum.composite inverted MRI at bed2562, while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807); MRI now enters as it is (strategy/aggressive.py:198-199)</t>
+          <t>DEFAULTS + config.json + validate_config (strategy/aggressive.py:50-130)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Done (owner decision 6.1 (2)): STRONG / WEAK fixtures mirrored, so scenario results are unchanged; a test pins the direction against determine_signal</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29596,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Volatility-aware trail that never moves down</t>
+          <t>Reuse existing indicators; formulas unchanged</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -29558,12 +29606,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4 × ATR%, clamped 3–20%; ratchet is one-way; tightens ×0.5 on fading momentum</t>
+          <t>strategy/live.py:57-83 reads ZPI, MSI, MRI, CRI, MH, RSI, MACD and volume from the stored scores, with no formula of its own. Fixed 2026-10-26: Momentum.composite inverted MRI at bed2562, while the engine scores MRI so that higher is more bullish (scores/engine.py:470-487) and sells on MRI &lt; 40 (:807); MRI now enters as it is (strategy/aggressive.py:198-199)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Done (owner decision 6.1 (2)): STRONG / WEAK fixtures mirrored, so scenario results are unchanged; a test pins the direction against determine_signal</t>
         </is>
       </c>
     </row>
@@ -29580,7 +29628,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Exits managed automatically while the market is open</t>
+          <t>Volatility-aware trail that never moves down</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -29590,76 +29638,76 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Scheduled 2026-10-26 (owner-approved): strategy/live.py schedule_jobs runs run_once through the scheduler's run_job every manage_interval_minutes (default 2, null = off), 09:15–15:30 on trading days, only while a position is open (no Dhan call otherwise). At bed2562 only python -m strategy.live --manage ran a pass</t>
+          <t>4 × ATR%, clamped 3–20%; ratchet is one-way; tightens ×0.5 on fading momentum</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>The unattended pass manages only positions whose recorded mode (from the aggressive execution_mode) matches where orders now go (broker_env); the rest are reported as MODE_MISMATCH in pipeline_log, because the two switches can disagree</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Per user</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Same signal, private execution state per user (own entry, qty, trail)</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+          <t>Exits managed automatically while the market is open</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); one scheduled pass manages every open position for the one owner</t>
+          <t>Scheduled 2026-10-26 (owner-approved): strategy/live.py schedule_jobs runs run_once through the scheduler's run_job every manage_interval_minutes (default 2, null = off), 09:15–15:30 on trading days, only while a position is open (no Dhan call otherwise). At bed2562 only python -m strategy.live --manage ran a pass</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
+          <t>The unattended pass manages only positions whose recorded mode (from the aggressive execution_mode) matches where orders now go (broker_env); the rest are reported as MODE_MISMATCH in pipeline_log, because the two switches can disagree</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Per user</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Initial / remaining / partial quantity, T1 / T2 state, high water, trail, realised / unrealised P&amp;L, exit reason</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+          <t>Same signal, private execution state per user (own entry, qty, trail)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>strategy_position columns (strategy/positions.py:37-84): initial_qty, remaining_qty, t1_state/qty/price/at, t2_state/at, high_water, trail_pct/stop/moves, realized_pnl, unrealized_pnl, exit_reason, mode</t>
+          <t>strategy_position / strategy_event have no tenant or user column; config is global; orders go to the owner's book (strategy/live.py:102-187); one scheduled pass manages every open position for the one owner</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -29676,7 +29724,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Machine-readable exit reasons</t>
+          <t>Initial / remaining / partial quantity, T1 / T2 state, high water, trail, realised / unrealised P&amp;L, exit reason</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -29686,7 +29734,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>The 8 constants in strategy/aggressive.py</t>
+          <t>strategy_position columns (strategy/positions.py:37-84): initial_qty, remaining_qty, t1_state/qty/price/at, t2_state/at, high_water, trail_pct/stop/moves, realized_pnl, unrealized_pnl, exit_reason, mode</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -29698,17 +29746,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Aggressive strategy tests (config, entry, SL, +3%, runner, +6%, trail, idempotency, broker, edge cases)</t>
+          <t>Machine-readable exit reasons</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -29718,7 +29766,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py, test_aggressive_backtest.py, test_strategy_live.py, test_paper_broker.py</t>
+          <t>The 8 constants in strategy/aggressive.py</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -29740,22 +29788,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Authentication tests</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+          <t>Aggressive strategy tests (config, entry, SL, +3%, runner, +6%, trail, idempotency, broker, edge cases)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Only route labels are checked (tests/test_w39_ops_tests.py:722-750)</t>
+          <t>tests/test_aggressive_decisions.py, test_aggressive_lifecycle.py, test_aggressive_backtest.py, test_strategy_live.py, test_paper_broker.py</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26); PR #11 tests the owner gate (tests/test_owner_gate.py there)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -29772,22 +29820,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Authorization / cross-user security tests</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Authentication tests</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>tests/test_wealth_api_security.py (8), cross-owner wealth tests, tenant book test</t>
+          <t>Only route labels are checked (tests/test_w39_ops_tests.py:722-750)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Only if enterprise mode is ever switched on (with the /api/orders fix, row P3)</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26); PR #11 tests the owner gate (tests/test_owner_gate.py there)</t>
         </is>
       </c>
     </row>
@@ -29804,22 +29852,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Dhan isolation and personalization tests</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+          <t>Authorization / cross-user security tests</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tests/test_wealth_api_security.py (8), cross-owner wealth tests, tenant book test</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
+          <t>tests/test_enterprise_owner_book.py (7) and tests/test_wealth_api_security.py (8); the owner-book scan covers every GET route</t>
         </is>
       </c>
     </row>
@@ -29836,39 +29884,39 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Full regression stays green</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+          <t>Dhan isolation and personalization tests</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1,315 test functions in 85 files; CI python -m pytest tests/ -v + scenario replay</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>master green from run 169 (#16); this branch 1,578 passed, 0 failed</t>
+          <t>Not planned: ATIP stays single-owner (owner decision 2026-10-26)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Backtest</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>The 7 deterministic scenarios and the full metric list</t>
+          <t>Full regression stays green</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -29878,12 +29926,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>strategy/backtest_aggressive.scenarios() and metrics(): win rate, PF, expectancy, drawdown, T1 / T2 rates, runner success, trailing / initial-stop exit rates, profit after +3%</t>
+          <t>1,315 test functions in 85 files; CI python -m pytest tests/ -v + scenario replay</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>master green from run 169 (#16); this branch 1,578 passed, 0 failed</t>
         </is>
       </c>
     </row>
@@ -29900,7 +29948,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Do not claim profitability unless shown after costs</t>
+          <t>The 7 deterministic scenarios and the full metric list</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -29910,44 +29958,44 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Costs on every leg, same-bar ambiguity against the strategy; the real-bars comparison is strategy/backtest_history.py</t>
+          <t>strategy/backtest_aggressive.scenarios() and metrics(): win rate, PF, expectancy, drawdown, T1 / T2 rates, runner success, trailing / initial-stop exit rates, profit after +3%</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Run it on the real database (§7.8)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Backtest</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Private dashboard at /dhan after login, with aggressive-trade state</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+          <t>Do not claim profitability unless shown after costs</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>No /dhan base path anywhere; strategy_position is not shown in any page or API, only via python -m strategy.live status</t>
+          <t>Costs on every leg, same-bar ambiguity against the strategy; the real-bars comparison is strategy/backtest_history.py</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Single-owner: the existing dashboard behind the owner gate. Still worth adding: a read-only "Aggressive positions" panel and API</t>
+          <t>Run it on the real database (§7.8)</t>
         </is>
       </c>
     </row>
@@ -29959,44 +30007,44 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>App works under a base path</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Private dashboard at /dhan after login, with aggressive-trade state</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ATIP_ROOT_PATH / dashboard_root_path (dashboard/security.py:86-102, main.py:481-487); docs use /ATIP</t>
+          <t>No /dhan base path anywhere; strategy_position is not shown in any page or API, only via python -m strategy.live status</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Page JavaScript calls absolute /api/... and the login redirect is a bare /login (enterprise/authz.py:265), so the browser leaves the prefix (also PR #14's open D10)</t>
+          <t>Single-owner: the existing dashboard behind the owner gate. Still worth adding: a read-only "Aggressive positions" panel and API</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Deploy</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Container, health check, test/production separation, externalized secrets</t>
+          <t>App works under a base path</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -30006,12 +30054,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Dockerfile (non-root, HEALTHCHECK), docker-compose.yml on 127.0.0.1, /health/live and /health/ready; CI builds and boots the image</t>
+          <t>ATIP_ROOT_PATH / dashboard_root_path (dashboard/security.py:86-102, main.py:481-487); docs use /ATIP</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>No deploy workflow, no TLS proxy, no trusted-hosts check, rate limiting off; HSTS / Secure cookies only with ops.tls_enabled; Python 3.12 in CI vs 3.14 in Docker</t>
+          <t>Page JavaScript calls absolute /api/... and the login redirect is a bare /login (enterprise/authz.py:265), so the browser leaves the prefix (also PR #14's open D10)</t>
         </is>
       </c>
     </row>
@@ -30028,123 +30076,155 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Deploy to test.bkesari.com/dhan</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+          <t>Container, health check, test/production separation, externalized secrets</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>test.bkesari.com receives only the snapshot</t>
+          <t>Dockerfile (non-root, HEALTHCHECK), docker-compose.yml on 127.0.0.1, /health/live and /health/ready; CI builds and boots the image</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Needs 6.1 (3) and the owner's hosting credentials</t>
+          <t>No deploy workflow, no TLS proxy, no trusted-hosts check, rate limiting off; HSTS / Secure cookies only with ops.tls_enabled; Python 3.12 in CI vs 3.14 in Docker</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Deploy</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Grouped commits, no secrets committed, push to the branch</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>PRESENT</t>
+          <t>Deploy to test.bkesari.com/dhan</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Branch per change with draft PRs; atip_data/, .env and deploy/atip.env are git-ignored</t>
+          <t>test.bkesari.com receives only the snapshot</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Needs 6.1 (3) and the owner's hosting credentials</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Post-deployment checks on the test URL</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
+          <t>Grouped commits, no secrets committed, push to the branch</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nothing is deployed</t>
+          <t>Branch per change with draft PRs; atip_data/, .env and deploy/atip.env are git-ignored</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>After P10</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Post-deployment checks on the test URL</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Nothing is deployed</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>After P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Paper by default; no live orders from a test deployment</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>PRESENT</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>broker_env falls back to PAPER (orders/environment.py:43-53); LIVE needs confirm, no halt, execution.live_trading_enabled and environment production (ops/trading_safety.py:24-42); the execution layer's Dhan adapter refuses every call (execution/adapters.py:240-260)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>deploy/atip.env.example:5 sets ATIP_ENV=production, so a container built from the example already meets one LIVE condition: set it to staging for test.bkesari.com</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30887,7 +30967,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). Decided 2026-10-26: ATIP stays single-owner, in line with PR #11's owner-only gate, so the prompt's multi-user phases (3, 5 and the per-user parts of 7 and 9) are not planned. See §6.</t>
+          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). Decided 2026-10-26: ATIP stays single-owner, in line with PR #11's owner-only gate, so the prompt's multi-user phases (3, 5 and the per-user parts of 7 and 9) are not planned. See §6. 4. Open: the owner's dashboard token reaches other tenants. Measured 2026-10-26: 18 pages give another tenant's viewer the install-wide X-ATIP-Token, which guards the write routes. The owner-book read leak found in the same review is fixed (OWNER_BOOK, tests/test_enterprise_owner_book.py). The token is latent while enterprise mode is off; it should be scoped (R12) before that mode is switched on.</t>
         </is>
       </c>
     </row>
@@ -34860,7 +34940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35175,27 +35255,54 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Done 2026-10-26: close the owner-book read leak in enterprise/authz.py (OWNER_BOOK)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Review row P3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Close the latent /api/orders read leak in enterprise/authz.py (enterprise mode only)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Review row P3; matters only if enterprise mode is ever switched on</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Stop the install-wide dashboard token reaching other tenants: per-session tokens, or no token in the 18 pages another tenant can open. Needed before enterprise mode is ever switched on</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Review row P3 (secrets); the token guards the write routes</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
+++ b/docs/master/ATIP_MASTER_FILE_2026-10-26.xlsx
@@ -3354,7 +3354,7 @@
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>X-ATIP-Token header required by state-changing routes</t>
+          <t>X-ATIP-Token required by state-changing routes; the owner's pages carry the install's token, another tenant's pages carry its own per-session token (R12)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -26896,21 +26896,21 @@
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
-      <c r="G348" s="6" t="inlineStr">
-        <is>
-          <t>DEFECT</t>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr"/>
       <c r="I348" s="2" t="inlineStr"/>
       <c r="J348" s="2" t="inlineStr">
         <is>
-          <t>Measured 2026-10-26: 18 HTML pages return the token to another tenant's VIEWER (/backtests, /strategies, /trading, /market, /execution-lab, /data-platform, /assistant, /strategy-builder, /brokers, /compliance, /research, /options-builder, /market-pulse, /signals, /screener, /baskets, /ml, /wealth); the token is the X-ATIP-Token that guards the write routes (dashboard/security.py)</t>
+          <t>Fixed 2026-10-26 (R12). Measured before the fix: 18 HTML pages returned the token to another tenant's VIEWER (/backtests, /strategies, /trading, /market, /execution-lab, /data-platform, /assistant, /strategy-builder, /brokers, /compliance, /research, /options-builder, /market-pulse, /signals, /screener, /baskets, /ml, /wealth); the token is the X-ATIP-Token that guards the write routes (dashboard/security.py)</t>
         </is>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
-          <t>Open (R12). Per-user or per-session tokens, or no token in pages served to other tenants. Enterprise mode is off, so this is latent</t>
+          <t>Done 2026-10-26. The install's token now goes only to the owner's requests; another tenant's pages carry a per-session token (session_token) that the write guard accepts for its session alone. tests/test_enterprise_owner_book.py scans every GET route as another tenant and as an anonymous visitor. Enterprise mode is still off</t>
         </is>
       </c>
       <c r="L348" s="2" t="inlineStr"/>
@@ -29407,19 +29407,19 @@
           <t>The install-wide dashboard token must not reach another tenant</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>DEFECT</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Measured 2026-10-26: 18 HTML pages return the token to another tenant's VIEWER (/backtests, /strategies, /trading, /market, /execution-lab, /data-platform, /assistant, /strategy-builder, /brokers, /compliance, /research, /options-builder, /market-pulse, /signals, /screener, /baskets, /ml, /wealth); the token is the X-ATIP-Token that guards the write routes (dashboard/security.py)</t>
+          <t>Fixed 2026-10-26 (R12). Measured before the fix: 18 HTML pages returned the token to another tenant's VIEWER (/backtests, /strategies, /trading, /market, /execution-lab, /data-platform, /assistant, /strategy-builder, /brokers, /compliance, /research, /options-builder, /market-pulse, /signals, /screener, /baskets, /ml, /wealth); the token is the X-ATIP-Token that guards the write routes (dashboard/security.py)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Open (R12). Per-user or per-session tokens, or no token in pages served to other tenants. Enterprise mode is off, so this is latent</t>
+          <t>Done 2026-10-26. The install's token now goes only to the owner's requests; another tenant's pages carry a per-session token (session_token) that the write guard accepts for its session alone. tests/test_enterprise_owner_book.py scans every GET route as another tenant and as an anonymous visitor. Enterprise mode is still off</t>
         </is>
       </c>
     </row>
@@ -30967,7 +30967,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). Decided 2026-10-26: ATIP stays single-owner, in line with PR #11's owner-only gate, so the prompt's multi-user phases (3, 5 and the per-user parts of 7 and 9) are not planned. See §6. 4. Open: the owner's dashboard token reaches other tenants. Measured 2026-10-26: 18 pages give another tenant's viewer the install-wide X-ATIP-Token, which guards the write routes. The owner-book read leak found in the same review is fixed (OWNER_BOOK, tests/test_enterprise_owner_book.py). The token is latent while enterprise mode is off; it should be scoped (R12) before that mode is switched on.</t>
+          <t>1. Fixed (owner-approved, 2026-10-26): MRI was read the wrong way round at the +6% runner checkpoint. The score engine scores MRI so that higher is more bullish (scores/engine.py:470-487), and the signal engine sells on low MRI (scores/engine.py:807). But Momentum.composite inverted MRI as a risk measure, so strong momentum pushed a runner toward exit and weak momentum toward holding. MRI now enters as it is (strategy/aggressive.py:198-199). The test fixtures are mirrored, so every existing result is unchanged, and test_mri_counts_as_strength_the_way_the_score_engine_reads_it pins the direction against determine_signal. 2. Index names disagree across documents. The code defines VPI as Volatility-Potential and SPI as Stability Profit. The strategy library and the formulas workbook call them "value/profit" and "stock/sector strength". §4 fixes the canonical meanings from the code. 3. The consolidated prompt's aggressive-strategy logic (phases 4, 6, 8, 13) is already built and tested. Nothing scheduled it: exits ran only when python -m strategy.live --manage was run by hand. Scheduled (owner-approved, 2026-10-26): a management pass now runs every manage_interval_minutes (default 2) from 09:15 to 15:30 on trading days while a position is open. Unattended, it never sells a position through a broker other than the one it was opened with (PAPER vs LIVE). Decided 2026-10-26: ATIP stays single-owner, in line with PR #11's owner-only gate, so the prompt's multi-user phases (3, 5 and the per-user parts of 7 and 9) are not planned. See §6. 4. Fixed: the owner's dashboard token reached other tenants (R12). Measured 2026-10-26: 18 pages gave another tenant's viewer the install-wide X-ATIP-Token, which guards the write routes. Now the install's token goes only to the owner's requests, and another tenant's pages carry a per-session token that the write guard accepts for its session alone. The owner-book read leak found in the same review is fixed too (OWNER_BOOK, tests/test_enterprise_owner_book.py). Enterprise mode is still off.</t>
         </is>
       </c>
     </row>
@@ -35282,12 +35282,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Stop the install-wide dashboard token reaching other tenants: per-session tokens, or no token in the 18 pages another tenant can open. Needed before enterprise mode is ever switched on</t>
+          <t>Done 2026-10-26: the install's dashboard token goes only to the owner's requests; another tenant's pages carry a per-session token that the write guard accepts for its session alone (dashboard/security.py: session_token, guard_ok)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
